--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260824.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260824.xlsx
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>202609WTX</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>115/09台股期貨</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>26,162,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>202609WTX</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>115/09台股期貨</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>26,162,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>41,037,000</t>
+          <t>18,002,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,002,000</t>
+          <t>41,037,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,264,000</t>
+          <t>2,545,761,747</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,545,761,747</t>
+          <t>14,264,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
